--- a/emergency_contact_form_templates/011_emergency_department_patient_satisfaction_survey--emergency_contact_form_templates.xlsx
+++ b/emergency_contact_form_templates/011_emergency_department_patient_satisfaction_survey--emergency_contact_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_30_minutes'}</t>
+          <t>less_than_30_minutes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 30 minutes'}</t>
+          <t>Less than 30 minutes</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '30-60 minutes'}</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'60-90_minutes'}</t>
+          <t>60-90_minutes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '60-90 minutes'}</t>
+          <t>60-90 minutes</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_90_minutes'}</t>
+          <t>more_than_90_minutes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'More than 90 minutes'}</t>
+          <t>More than 90 minutes</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Very helpful'}</t>
+          <t>Very helpful</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat helpful'}</t>
+          <t>Somewhat helpful</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_helpful_at_all'}</t>
+          <t>not_helpful_at_all</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not helpful at all'}</t>
+          <t>Not helpful at all</t>
         </is>
       </c>
     </row>
